--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/95.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/95.xlsx
@@ -426,13 +426,13 @@
         <v>-4.808674055564616</v>
       </c>
       <c r="E2">
-        <v>-5.69979929914239</v>
+        <v>-6.252977975130278</v>
       </c>
       <c r="F2">
-        <v>0.6687814470352703</v>
+        <v>-0.1826990630371471</v>
       </c>
       <c r="G2">
-        <v>-10.31410885652212</v>
+        <v>-10.43167721232143</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.727963404649412</v>
       </c>
       <c r="E3">
-        <v>-7.196259484436661</v>
+        <v>-6.364774117572012</v>
       </c>
       <c r="F3">
-        <v>1.126997846098234</v>
+        <v>0.07340231668195923</v>
       </c>
       <c r="G3">
-        <v>-10.39456547795875</v>
+        <v>-9.61790681789912</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.583622314797291</v>
       </c>
       <c r="E4">
-        <v>-7.172021343144962</v>
+        <v>-7.872854988153154</v>
       </c>
       <c r="F4">
-        <v>1.251791395329979</v>
+        <v>0.252356183443542</v>
       </c>
       <c r="G4">
-        <v>-10.3735450678834</v>
+        <v>-9.514418207679684</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.376589714314521</v>
       </c>
       <c r="E5">
-        <v>-8.467025859917099</v>
+        <v>-8.189566424150604</v>
       </c>
       <c r="F5">
-        <v>1.486154757664821</v>
+        <v>0.01328272405638232</v>
       </c>
       <c r="G5">
-        <v>-9.876860047030169</v>
+        <v>-9.077832527313879</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.105465344421096</v>
       </c>
       <c r="E6">
-        <v>-9.99355529520313</v>
+        <v>-9.62342110193441</v>
       </c>
       <c r="F6">
-        <v>1.68538540171213</v>
+        <v>0.5189977099958692</v>
       </c>
       <c r="G6">
-        <v>-9.296332269005628</v>
+        <v>-9.141183550189538</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.777524244783943</v>
       </c>
       <c r="E7">
-        <v>-9.577939284716212</v>
+        <v>-10.68278902098108</v>
       </c>
       <c r="F7">
-        <v>1.402464798959987</v>
+        <v>0.6188880499972533</v>
       </c>
       <c r="G7">
-        <v>-8.75838965137903</v>
+        <v>-8.642986908218051</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.393425245409634</v>
       </c>
       <c r="E8">
-        <v>-11.04070446653215</v>
+        <v>-11.04450050168304</v>
       </c>
       <c r="F8">
-        <v>1.945487795986758</v>
+        <v>0.7600393703320807</v>
       </c>
       <c r="G8">
-        <v>-8.610607148426768</v>
+        <v>-8.132370954226635</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.958660946631003</v>
       </c>
       <c r="E9">
-        <v>-12.66390820182621</v>
+        <v>-12.40511745096482</v>
       </c>
       <c r="F9">
-        <v>1.492811518113718</v>
+        <v>0.7802399378167494</v>
       </c>
       <c r="G9">
-        <v>-8.104958136019947</v>
+        <v>-7.418434127596206</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.477931237782144</v>
       </c>
       <c r="E10">
-        <v>-11.4766836721447</v>
+        <v>-12.84597252667272</v>
       </c>
       <c r="F10">
-        <v>1.70281093839742</v>
+        <v>1.321564781667782</v>
       </c>
       <c r="G10">
-        <v>-8.774957436554235</v>
+        <v>-6.78189543511392</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.957909386867879</v>
       </c>
       <c r="E11">
-        <v>-14.37733214672953</v>
+        <v>-13.91831923110948</v>
       </c>
       <c r="F11">
-        <v>2.159297706323339</v>
+        <v>1.320429918325946</v>
       </c>
       <c r="G11">
-        <v>-7.178953136997975</v>
+        <v>-6.855171203552697</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.415034532988052</v>
       </c>
       <c r="E12">
-        <v>-14.9110031891247</v>
+        <v>-14.67756779340138</v>
       </c>
       <c r="F12">
-        <v>2.318574533798822</v>
+        <v>1.043200199631036</v>
       </c>
       <c r="G12">
-        <v>-6.661064953948014</v>
+        <v>-5.740981123658688</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.8672386028901369</v>
       </c>
       <c r="E13">
-        <v>-15.48025479293967</v>
+        <v>-15.39125562745992</v>
       </c>
       <c r="F13">
-        <v>2.408415948836845</v>
+        <v>1.652272243152622</v>
       </c>
       <c r="G13">
-        <v>-5.283244495987979</v>
+        <v>-5.070019763742574</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.3404806090106328</v>
       </c>
       <c r="E14">
-        <v>-16.95540900413757</v>
+        <v>-16.07768178238228</v>
       </c>
       <c r="F14">
-        <v>2.276094196648458</v>
+        <v>1.748465579435312</v>
       </c>
       <c r="G14">
-        <v>-4.962611120519583</v>
+        <v>-4.364481702461755</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.1441538375747689</v>
       </c>
       <c r="E15">
-        <v>-18.15900964607288</v>
+        <v>-17.2331923903874</v>
       </c>
       <c r="F15">
-        <v>2.542054805195684</v>
+        <v>1.506974943966784</v>
       </c>
       <c r="G15">
-        <v>-4.3226340774108</v>
+        <v>-4.014566215659433</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.5737776384505362</v>
       </c>
       <c r="E16">
-        <v>-18.1839704461351</v>
+        <v>-18.09965610302976</v>
       </c>
       <c r="F16">
-        <v>2.747249694543149</v>
+        <v>1.70622546883176</v>
       </c>
       <c r="G16">
-        <v>-4.282021334551442</v>
+        <v>-3.573259003700598</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.9389781241301217</v>
       </c>
       <c r="E17">
-        <v>-18.37158761452291</v>
+        <v>-18.72205219895724</v>
       </c>
       <c r="F17">
-        <v>2.512341266457265</v>
+        <v>2.330107064780596</v>
       </c>
       <c r="G17">
-        <v>-3.693556892969916</v>
+        <v>-2.358442995031311</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.240300580923272</v>
       </c>
       <c r="E18">
-        <v>-19.50455874466818</v>
+        <v>-19.27565450250026</v>
       </c>
       <c r="F18">
-        <v>2.895696446594432</v>
+        <v>2.44114971512587</v>
       </c>
       <c r="G18">
-        <v>-3.407803065238794</v>
+        <v>-2.00489596250275</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.478039456006761</v>
       </c>
       <c r="E19">
-        <v>-21.01168022343329</v>
+        <v>-19.79702373295128</v>
       </c>
       <c r="F19">
-        <v>3.321058137727561</v>
+        <v>2.636904529551032</v>
       </c>
       <c r="G19">
-        <v>-2.13863657567171</v>
+        <v>-1.650411672665979</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.656820602758797</v>
       </c>
       <c r="E20">
-        <v>-21.03340151866214</v>
+        <v>-20.7619725457393</v>
       </c>
       <c r="F20">
-        <v>3.721978020273688</v>
+        <v>2.75625404821158</v>
       </c>
       <c r="G20">
-        <v>-2.535226954273956</v>
+        <v>-1.44946527223258</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.781854928306175</v>
       </c>
       <c r="E21">
-        <v>-21.99016850514024</v>
+        <v>-22.08202508001148</v>
       </c>
       <c r="F21">
-        <v>3.526895840179599</v>
+        <v>2.901801514353064</v>
       </c>
       <c r="G21">
-        <v>-2.515659423563562</v>
+        <v>-1.161883923287679</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.855547612146355</v>
       </c>
       <c r="E22">
-        <v>-20.09525337855325</v>
+        <v>-22.00428111722201</v>
       </c>
       <c r="F22">
-        <v>4.099440194707339</v>
+        <v>3.082243128970075</v>
       </c>
       <c r="G22">
-        <v>-2.02574536880738</v>
+        <v>-0.7596465041348547</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.880958283298798</v>
       </c>
       <c r="E23">
-        <v>-23.98812065148491</v>
+        <v>-23.00898031559996</v>
       </c>
       <c r="F23">
-        <v>4.036573735774079</v>
+        <v>3.539402531227066</v>
       </c>
       <c r="G23">
-        <v>-1.813833841091306</v>
+        <v>-0.7972464477360682</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.859462841743239</v>
       </c>
       <c r="E24">
-        <v>-24.03712854511789</v>
+        <v>-22.75369902830805</v>
       </c>
       <c r="F24">
-        <v>4.598082579761724</v>
+        <v>3.649051867600831</v>
       </c>
       <c r="G24">
-        <v>-1.107768409403082</v>
+        <v>-0.2083695085091467</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.793731965616155</v>
       </c>
       <c r="E25">
-        <v>-23.81316662442651</v>
+        <v>-24.09997078567387</v>
       </c>
       <c r="F25">
-        <v>4.523541110653407</v>
+        <v>4.032062446898433</v>
       </c>
       <c r="G25">
-        <v>-1.503382369528252</v>
+        <v>-1.012813017879701</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.685968008172929</v>
       </c>
       <c r="E26">
-        <v>-22.67979678599405</v>
+        <v>-23.20880377207143</v>
       </c>
       <c r="F26">
-        <v>4.700493641769826</v>
+        <v>4.209382773141694</v>
       </c>
       <c r="G26">
-        <v>-1.256455535356166</v>
+        <v>-0.7262472485807424</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.539666784800187</v>
       </c>
       <c r="E27">
-        <v>-23.34171068767727</v>
+        <v>-23.55003576773067</v>
       </c>
       <c r="F27">
-        <v>4.688934603031162</v>
+        <v>4.287559118413495</v>
       </c>
       <c r="G27">
-        <v>-1.580339287840498</v>
+        <v>-0.9558152419665159</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.359607939087817</v>
       </c>
       <c r="E28">
-        <v>-23.73754910583536</v>
+        <v>-23.13343129294845</v>
       </c>
       <c r="F28">
-        <v>4.566720589891735</v>
+        <v>4.493178131871194</v>
       </c>
       <c r="G28">
-        <v>-1.405596930868104</v>
+        <v>-1.051778380902067</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.154181821695469</v>
       </c>
       <c r="E29">
-        <v>-23.41490273085473</v>
+        <v>-23.09312022382966</v>
       </c>
       <c r="F29">
-        <v>5.413999620497153</v>
+        <v>3.837498824798496</v>
       </c>
       <c r="G29">
-        <v>-1.809379910818867</v>
+        <v>-1.199768438049323</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.9335856515468103</v>
       </c>
       <c r="E30">
-        <v>-23.18078205526282</v>
+        <v>-22.88523953738802</v>
       </c>
       <c r="F30">
-        <v>4.72424956214731</v>
+        <v>4.538178362660875</v>
       </c>
       <c r="G30">
-        <v>-1.906275085573445</v>
+        <v>-1.600081738438497</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.7083497184238413</v>
       </c>
       <c r="E31">
-        <v>-22.69441193664612</v>
+        <v>-22.3988154270241</v>
       </c>
       <c r="F31">
-        <v>5.081277569488703</v>
+        <v>4.419451776287232</v>
       </c>
       <c r="G31">
-        <v>-1.620338505720945</v>
+        <v>-1.932040523943142</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.4881218350177741</v>
       </c>
       <c r="E32">
-        <v>-22.95360970221735</v>
+        <v>-22.34004748677777</v>
       </c>
       <c r="F32">
-        <v>4.366651638032792</v>
+        <v>4.569195751691299</v>
       </c>
       <c r="G32">
-        <v>-2.782568896836028</v>
+        <v>-1.936922616328524</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.2791238198691741</v>
       </c>
       <c r="E33">
-        <v>-21.38155691759987</v>
+        <v>-21.98234800821559</v>
       </c>
       <c r="F33">
-        <v>4.524669347056021</v>
+        <v>4.634161293623253</v>
       </c>
       <c r="G33">
-        <v>-2.561851327614129</v>
+        <v>-2.65596083788999</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.08660362679415065</v>
       </c>
       <c r="E34">
-        <v>-21.98389300282843</v>
+        <v>-21.77935149829195</v>
       </c>
       <c r="F34">
-        <v>4.897759398337695</v>
+        <v>4.317521167372753</v>
       </c>
       <c r="G34">
-        <v>-2.693978500625781</v>
+        <v>-2.708891073730221</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.08828148451073942</v>
       </c>
       <c r="E35">
-        <v>-20.77853970571404</v>
+        <v>-20.52896493078244</v>
       </c>
       <c r="F35">
-        <v>4.26966141230861</v>
+        <v>4.317044027748741</v>
       </c>
       <c r="G35">
-        <v>-3.284218248529264</v>
+        <v>-3.174415552516221</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.2446487536274583</v>
       </c>
       <c r="E36">
-        <v>-21.33435982410452</v>
+        <v>-19.56992613770966</v>
       </c>
       <c r="F36">
-        <v>4.637670257941512</v>
+        <v>4.364376941144704</v>
       </c>
       <c r="G36">
-        <v>-2.956434043625809</v>
+        <v>-3.443358795825166</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.3817394281446652</v>
       </c>
       <c r="E37">
-        <v>-19.43158682169095</v>
+        <v>-19.72890691401277</v>
       </c>
       <c r="F37">
-        <v>4.531329420974529</v>
+        <v>4.327357201913594</v>
       </c>
       <c r="G37">
-        <v>-3.892393811773695</v>
+        <v>-3.268256156099198</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.4978010968901311</v>
       </c>
       <c r="E38">
-        <v>-20.37850239090655</v>
+        <v>-18.91398455391154</v>
       </c>
       <c r="F38">
-        <v>4.218251274556066</v>
+        <v>4.385258426634475</v>
       </c>
       <c r="G38">
-        <v>-4.094656027481014</v>
+        <v>-3.686220700668888</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.5873039251948289</v>
       </c>
       <c r="E39">
-        <v>-19.42828086547638</v>
+        <v>-18.31905779768648</v>
       </c>
       <c r="F39">
-        <v>5.330763607129053</v>
+        <v>4.103832198676982</v>
       </c>
       <c r="G39">
-        <v>-4.248710844313427</v>
+        <v>-4.095402700434073</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.6471149835451826</v>
       </c>
       <c r="E40">
-        <v>-18.39372007767292</v>
+        <v>-17.55126192648807</v>
       </c>
       <c r="F40">
-        <v>5.019830932283842</v>
+        <v>3.990398880007229</v>
       </c>
       <c r="G40">
-        <v>-4.214303841347146</v>
+        <v>-4.328419487424707</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.6780633841756817</v>
       </c>
       <c r="E41">
-        <v>-17.63144797753654</v>
+        <v>-16.65656883647086</v>
       </c>
       <c r="F41">
-        <v>4.450321715919959</v>
+        <v>4.166064128179698</v>
       </c>
       <c r="G41">
-        <v>-3.793540578575782</v>
+        <v>-4.65277317393544</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.6841453920038009</v>
       </c>
       <c r="E42">
-        <v>-17.42134116982479</v>
+        <v>-16.71015772219512</v>
       </c>
       <c r="F42">
-        <v>4.689260979787865</v>
+        <v>3.883436767488145</v>
       </c>
       <c r="G42">
-        <v>-4.189540928900436</v>
+        <v>-4.16919539630189</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.6707761358452851</v>
       </c>
       <c r="E43">
-        <v>-16.97259499259971</v>
+        <v>-15.12719445142732</v>
       </c>
       <c r="F43">
-        <v>5.073658246117754</v>
+        <v>3.812200484316999</v>
       </c>
       <c r="G43">
-        <v>-4.943228952675157</v>
+        <v>-4.553742410105331</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.644164380507887</v>
       </c>
       <c r="E44">
-        <v>-15.97200332022202</v>
+        <v>-15.85636545730482</v>
       </c>
       <c r="F44">
-        <v>4.127231921071262</v>
+        <v>3.951122667970893</v>
       </c>
       <c r="G44">
-        <v>-4.808665954959996</v>
+        <v>-4.572328300849466</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.6133108136155814</v>
       </c>
       <c r="E45">
-        <v>-14.58517545426925</v>
+        <v>-14.47812643237179</v>
       </c>
       <c r="F45">
-        <v>4.614416328210124</v>
+        <v>3.569611433672358</v>
       </c>
       <c r="G45">
-        <v>-4.318827611796957</v>
+        <v>-4.42220526537127</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.5899008386753437</v>
       </c>
       <c r="E46">
-        <v>-14.11133142100823</v>
+        <v>-14.30436437696362</v>
       </c>
       <c r="F46">
-        <v>4.675193644553524</v>
+        <v>3.667266010053587</v>
       </c>
       <c r="G46">
-        <v>-5.100570696947782</v>
+        <v>-4.70303000731437</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.583604225042578</v>
       </c>
       <c r="E47">
-        <v>-14.98542042964297</v>
+        <v>-12.863416014237</v>
       </c>
       <c r="F47">
-        <v>4.520303850843267</v>
+        <v>3.70170952666199</v>
       </c>
       <c r="G47">
-        <v>-3.950240079678992</v>
+        <v>-4.725492853776309</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.6033009635444667</v>
       </c>
       <c r="E48">
-        <v>-14.49088094435034</v>
+        <v>-11.92014696456459</v>
       </c>
       <c r="F48">
-        <v>4.657834377260458</v>
+        <v>3.497278392059906</v>
       </c>
       <c r="G48">
-        <v>-5.286265127479896</v>
+        <v>-5.327935221898655</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.6535698057900612</v>
       </c>
       <c r="E49">
-        <v>-13.21313302063287</v>
+        <v>-11.49144418519314</v>
       </c>
       <c r="F49">
-        <v>4.00316733515398</v>
+        <v>3.76251666423189</v>
       </c>
       <c r="G49">
-        <v>-4.633581590446166</v>
+        <v>-5.180146192084915</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.7365202608788577</v>
       </c>
       <c r="E50">
-        <v>-12.2318662405496</v>
+        <v>-10.40437434660987</v>
       </c>
       <c r="F50">
-        <v>4.022647222998214</v>
+        <v>3.506513031866314</v>
       </c>
       <c r="G50">
-        <v>-4.872939876048614</v>
+        <v>-5.308344194486941</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.8549406429032119</v>
       </c>
       <c r="E51">
-        <v>-11.33451094207317</v>
+        <v>-10.19848304839282</v>
       </c>
       <c r="F51">
-        <v>4.160384841266104</v>
+        <v>3.44888848185797</v>
       </c>
       <c r="G51">
-        <v>-5.535899303792966</v>
+        <v>-5.120360140948421</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.007120239739941</v>
       </c>
       <c r="E52">
-        <v>-11.05703489346138</v>
+        <v>-9.279099117049499</v>
       </c>
       <c r="F52">
-        <v>4.096863972084632</v>
+        <v>3.510964678288959</v>
       </c>
       <c r="G52">
-        <v>-4.623334417926046</v>
+        <v>-5.474374496758791</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.195063418052749</v>
       </c>
       <c r="E53">
-        <v>-11.07660897843529</v>
+        <v>-8.312077851810397</v>
       </c>
       <c r="F53">
-        <v>3.842427610845153</v>
+        <v>3.089910497650387</v>
       </c>
       <c r="G53">
-        <v>-5.335297521645595</v>
+        <v>-5.348053619717774</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.416648787516367</v>
       </c>
       <c r="E54">
-        <v>-10.48148702127796</v>
+        <v>-8.019558871780072</v>
       </c>
       <c r="F54">
-        <v>3.502773781410077</v>
+        <v>3.470094687369637</v>
       </c>
       <c r="G54">
-        <v>-5.230854684278108</v>
+        <v>-5.743886882388598</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.669744776533729</v>
       </c>
       <c r="E55">
-        <v>-10.1698092774062</v>
+        <v>-7.850469179112328</v>
       </c>
       <c r="F55">
-        <v>3.867971148077879</v>
+        <v>3.25192425102472</v>
       </c>
       <c r="G55">
-        <v>-5.59849712685409</v>
+        <v>-5.973261680674629</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.953542771282118</v>
       </c>
       <c r="E56">
-        <v>-10.15239070910987</v>
+        <v>-7.10012094868953</v>
       </c>
       <c r="F56">
-        <v>3.733858465564639</v>
+        <v>3.244203866830628</v>
       </c>
       <c r="G56">
-        <v>-5.335185259628177</v>
+        <v>-5.825658013726857</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.261874986186165</v>
       </c>
       <c r="E57">
-        <v>-8.868699539986567</v>
+        <v>-6.412731248739808</v>
       </c>
       <c r="F57">
-        <v>4.088116412311069</v>
+        <v>3.043266785933552</v>
       </c>
       <c r="G57">
-        <v>-5.242780565570313</v>
+        <v>-6.010052293452597</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.59550299690405</v>
       </c>
       <c r="E58">
-        <v>-7.826554988303966</v>
+        <v>-6.44876451019402</v>
       </c>
       <c r="F58">
-        <v>3.693114386490542</v>
+        <v>2.973201814269965</v>
       </c>
       <c r="G58">
-        <v>-5.921595045216496</v>
+        <v>-6.463844086046135</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.949465074958166</v>
       </c>
       <c r="E59">
-        <v>-8.314436875842899</v>
+        <v>-5.616826443294966</v>
       </c>
       <c r="F59">
-        <v>3.712146955937264</v>
+        <v>2.888716622858443</v>
       </c>
       <c r="G59">
-        <v>-6.289164386943927</v>
+        <v>-6.260686384944063</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.321251662305601</v>
       </c>
       <c r="E60">
-        <v>-7.268720562420945</v>
+        <v>-5.389795299434538</v>
       </c>
       <c r="F60">
-        <v>3.503754568414992</v>
+        <v>2.766439653796402</v>
       </c>
       <c r="G60">
-        <v>-6.396839326115212</v>
+        <v>-6.492705867500892</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.707940916703856</v>
       </c>
       <c r="E61">
-        <v>-6.712136253146697</v>
+        <v>-4.866432527547595</v>
       </c>
       <c r="F61">
-        <v>3.530187772238324</v>
+        <v>2.485696000578816</v>
       </c>
       <c r="G61">
-        <v>-6.26921568752323</v>
+        <v>-6.981536463251762</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.099677985942514</v>
       </c>
       <c r="E62">
-        <v>-6.662198040176959</v>
+        <v>-4.743314731034377</v>
       </c>
       <c r="F62">
-        <v>3.525772573981403</v>
+        <v>2.780879754362003</v>
       </c>
       <c r="G62">
-        <v>-6.151029890628124</v>
+        <v>-6.673907206591701</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.492142789194965</v>
       </c>
       <c r="E63">
-        <v>-6.405845224363242</v>
+        <v>-4.165960211924662</v>
       </c>
       <c r="F63">
-        <v>3.779897469077429</v>
+        <v>2.546872590010365</v>
       </c>
       <c r="G63">
-        <v>-6.583233436197745</v>
+        <v>-7.072270280771312</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.872747793762914</v>
       </c>
       <c r="E64">
-        <v>-6.963459530046047</v>
+        <v>-4.041343106123182</v>
       </c>
       <c r="F64">
-        <v>3.220631844016566</v>
+        <v>2.194458589102566</v>
       </c>
       <c r="G64">
-        <v>-6.556264444571545</v>
+        <v>-7.068860648335319</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.230588246541113</v>
       </c>
       <c r="E65">
-        <v>-5.437598761783314</v>
+        <v>-3.111235583139154</v>
       </c>
       <c r="F65">
-        <v>3.834882840540455</v>
+        <v>2.477203577965316</v>
       </c>
       <c r="G65">
-        <v>-6.204385677836705</v>
+        <v>-7.060717735955636</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.55367888065365</v>
       </c>
       <c r="E66">
-        <v>-5.76592672985631</v>
+        <v>-4.217082090121976</v>
       </c>
       <c r="F66">
-        <v>3.252972964156664</v>
+        <v>2.677255962476202</v>
       </c>
       <c r="G66">
-        <v>-6.281465301144734</v>
+        <v>-7.306662930161464</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.825714407310323</v>
       </c>
       <c r="E67">
-        <v>-6.864152094058071</v>
+        <v>-3.611157630308766</v>
       </c>
       <c r="F67">
-        <v>3.279795500659312</v>
+        <v>2.120584784120906</v>
       </c>
       <c r="G67">
-        <v>-6.720075613940948</v>
+        <v>-6.968487961785377</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.03658296704556</v>
       </c>
       <c r="E68">
-        <v>-6.376344964322985</v>
+        <v>-3.53972654873304</v>
       </c>
       <c r="F68">
-        <v>3.021762368156877</v>
+        <v>2.21875294829187</v>
       </c>
       <c r="G68">
-        <v>-6.298395979818104</v>
+        <v>-6.571657394680749</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.17279749581579</v>
       </c>
       <c r="E69">
-        <v>-5.676499783610102</v>
+        <v>-3.682061254046239</v>
       </c>
       <c r="F69">
-        <v>3.107675664970825</v>
+        <v>2.331495408547688</v>
       </c>
       <c r="G69">
-        <v>-6.61577114603679</v>
+        <v>-7.126017679668562</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.225668611218535</v>
       </c>
       <c r="E70">
-        <v>-5.729785484907652</v>
+        <v>-3.5667348819784</v>
       </c>
       <c r="F70">
-        <v>3.377925559929747</v>
+        <v>1.848320299638376</v>
       </c>
       <c r="G70">
-        <v>-6.350360240159622</v>
+        <v>-6.843315812364451</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.191361237135807</v>
       </c>
       <c r="E71">
-        <v>-5.291542779123069</v>
+        <v>-3.536075875978516</v>
       </c>
       <c r="F71">
-        <v>3.790773933076187</v>
+        <v>1.956471947747879</v>
       </c>
       <c r="G71">
-        <v>-6.15228826952104</v>
+        <v>-6.913223720280691</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.066427717317215</v>
       </c>
       <c r="E72">
-        <v>-4.917130778189776</v>
+        <v>-3.590379114050649</v>
       </c>
       <c r="F72">
-        <v>3.230187890375261</v>
+        <v>1.934576540557083</v>
       </c>
       <c r="G72">
-        <v>-6.373191201608909</v>
+        <v>-6.518223285134433</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.856428342020941</v>
       </c>
       <c r="E73">
-        <v>-6.90149777029093</v>
+        <v>-3.857920681173454</v>
       </c>
       <c r="F73">
-        <v>2.783757502719329</v>
+        <v>2.15797563194847</v>
       </c>
       <c r="G73">
-        <v>-6.33375068307096</v>
+        <v>-6.189112821978693</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.567904470523795</v>
       </c>
       <c r="E74">
-        <v>-6.878891841049888</v>
+        <v>-4.610893741153544</v>
       </c>
       <c r="F74">
-        <v>2.584523545202408</v>
+        <v>1.9826649250244</v>
       </c>
       <c r="G74">
-        <v>-5.186774872601752</v>
+        <v>-6.586844095967255</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.21107021374356</v>
       </c>
       <c r="E75">
-        <v>-6.646187410519745</v>
+        <v>-4.771656245115007</v>
       </c>
       <c r="F75">
-        <v>2.604931204537777</v>
+        <v>2.004470868535694</v>
       </c>
       <c r="G75">
-        <v>-5.780622669530152</v>
+        <v>-5.985970785344168</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.801722613601923</v>
       </c>
       <c r="E76">
-        <v>-5.959566054665116</v>
+        <v>-5.441137297832069</v>
       </c>
       <c r="F76">
-        <v>2.895464503721648</v>
+        <v>2.06374386967561</v>
       </c>
       <c r="G76">
-        <v>-4.952755559688129</v>
+        <v>-6.390510881226354</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.351582669520287</v>
       </c>
       <c r="E77">
-        <v>-9.39003139153567</v>
+        <v>-5.484920451618411</v>
       </c>
       <c r="F77">
-        <v>3.101905257642924</v>
+        <v>1.766581974534537</v>
       </c>
       <c r="G77">
-        <v>-4.989452185660818</v>
+        <v>-5.475682479798938</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.877233296259434</v>
       </c>
       <c r="E78">
-        <v>-7.519611905342512</v>
+        <v>-6.564281929982801</v>
       </c>
       <c r="F78">
-        <v>2.690990294014618</v>
+        <v>1.957789051918331</v>
       </c>
       <c r="G78">
-        <v>-4.21963759254679</v>
+        <v>-5.568275147467363</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.389235709716655</v>
       </c>
       <c r="E79">
-        <v>-8.12728071391215</v>
+        <v>-7.211518382844082</v>
       </c>
       <c r="F79">
-        <v>2.760964145263898</v>
+        <v>2.12283462998691</v>
       </c>
       <c r="G79">
-        <v>-4.44610141061373</v>
+        <v>-4.653154342645743</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.893810681289219</v>
       </c>
       <c r="E80">
-        <v>-9.319854579780042</v>
+        <v>-7.249121558179079</v>
       </c>
       <c r="F80">
-        <v>2.899344576636361</v>
+        <v>1.876927139526654</v>
       </c>
       <c r="G80">
-        <v>-4.326623295146021</v>
+        <v>-4.359315038915942</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.399445473564255</v>
       </c>
       <c r="E81">
-        <v>-11.12459518208236</v>
+        <v>-8.319163230330554</v>
       </c>
       <c r="F81">
-        <v>3.146950220272355</v>
+        <v>2.023713843302727</v>
       </c>
       <c r="G81">
-        <v>-3.765422859329492</v>
+        <v>-4.172025443438657</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.906491845856298</v>
       </c>
       <c r="E82">
-        <v>-11.33819068730697</v>
+        <v>-9.173134083307824</v>
       </c>
       <c r="F82">
-        <v>2.644465867203786</v>
+        <v>2.122672269975961</v>
       </c>
       <c r="G82">
-        <v>-3.044290820605953</v>
+        <v>-3.826689202649147</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.421610770654695</v>
       </c>
       <c r="E83">
-        <v>-11.27700142485827</v>
+        <v>-10.60767404096023</v>
       </c>
       <c r="F83">
-        <v>2.42571557367691</v>
+        <v>2.240080095444346</v>
       </c>
       <c r="G83">
-        <v>-3.479601152239</v>
+        <v>-3.302292433333541</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.9482498927986351</v>
       </c>
       <c r="E84">
-        <v>-12.99342814154944</v>
+        <v>-11.3343655796768</v>
       </c>
       <c r="F84">
-        <v>2.852611401240024</v>
+        <v>2.044741121455389</v>
       </c>
       <c r="G84">
-        <v>-3.530095563375722</v>
+        <v>-3.215785411307003</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.4908962879039613</v>
       </c>
       <c r="E85">
-        <v>-13.32429787495323</v>
+        <v>-12.91030992330564</v>
       </c>
       <c r="F85">
-        <v>2.814120481501542</v>
+        <v>2.230141343345557</v>
       </c>
       <c r="G85">
-        <v>-2.309473258735799</v>
+        <v>-2.917392969010301</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.05987642502597994</v>
       </c>
       <c r="E86">
-        <v>-14.67950734309008</v>
+        <v>-14.67082297820986</v>
       </c>
       <c r="F86">
-        <v>2.621778540775913</v>
+        <v>2.076977867302735</v>
       </c>
       <c r="G86">
-        <v>-2.891658859575697</v>
+        <v>-2.59726346724799</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.3377945023665293</v>
       </c>
       <c r="E87">
-        <v>-16.39303096506519</v>
+        <v>-15.76313416948507</v>
       </c>
       <c r="F87">
-        <v>3.170402958180415</v>
+        <v>2.197586504415537</v>
       </c>
       <c r="G87">
-        <v>-2.13572820619721</v>
+        <v>-2.090322136268568</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.688440338776973</v>
       </c>
       <c r="E88">
-        <v>-18.39405648779023</v>
+        <v>-17.19915267036911</v>
       </c>
       <c r="F88">
-        <v>2.561161927708657</v>
+        <v>2.160831842753323</v>
       </c>
       <c r="G88">
-        <v>-1.307310229246462</v>
+        <v>-2.094000675397446</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.9826959987696035</v>
       </c>
       <c r="E89">
-        <v>-18.39795635322424</v>
+        <v>-18.70108263497818</v>
       </c>
       <c r="F89">
-        <v>2.568489665753821</v>
+        <v>2.127233260895775</v>
       </c>
       <c r="G89">
-        <v>-1.628875640533885</v>
+        <v>-1.462250088495262</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.211403807284373</v>
       </c>
       <c r="E90">
-        <v>-20.4840105714025</v>
+        <v>-19.89897261134185</v>
       </c>
       <c r="F90">
-        <v>2.84361201777601</v>
+        <v>2.34812239905668</v>
       </c>
       <c r="G90">
-        <v>-1.542710626048783</v>
+        <v>-1.765532455411119</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.365571077565822</v>
       </c>
       <c r="E91">
-        <v>-22.99277448501048</v>
+        <v>-21.46210014482227</v>
       </c>
       <c r="F91">
-        <v>2.66588413477057</v>
+        <v>2.41161013354204</v>
       </c>
       <c r="G91">
-        <v>-1.166515384192314</v>
+        <v>-1.499338326156618</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.440064717658461</v>
       </c>
       <c r="E92">
-        <v>-24.71734564910963</v>
+        <v>-23.83083853861365</v>
       </c>
       <c r="F92">
-        <v>2.575616938887508</v>
+        <v>2.38619250815454</v>
       </c>
       <c r="G92">
-        <v>-0.9326527159541588</v>
+        <v>-1.386567213543479</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.429989928022493</v>
       </c>
       <c r="E93">
-        <v>-26.53501935147747</v>
+        <v>-25.66676145154279</v>
       </c>
       <c r="F93">
-        <v>2.586978826184306</v>
+        <v>2.113303434650299</v>
       </c>
       <c r="G93">
-        <v>-1.639624076015499</v>
+        <v>-0.9109469854236429</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.337181291940057</v>
       </c>
       <c r="E94">
-        <v>-28.47615764350414</v>
+        <v>-28.60294480222285</v>
       </c>
       <c r="F94">
-        <v>2.508080144537264</v>
+        <v>2.482559801591818</v>
       </c>
       <c r="G94">
-        <v>-1.046431575979467</v>
+        <v>-0.8210172772381548</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.167024250368856</v>
       </c>
       <c r="E95">
-        <v>-31.65559873469074</v>
+        <v>-30.61386742753496</v>
       </c>
       <c r="F95">
-        <v>2.191903904032332</v>
+        <v>2.636091072761483</v>
       </c>
       <c r="G95">
-        <v>-1.704367931130517</v>
+        <v>-1.852710438797574</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.9277438452912643</v>
       </c>
       <c r="E96">
-        <v>-32.70320683587115</v>
+        <v>-32.83616774322421</v>
       </c>
       <c r="F96">
-        <v>1.798414477089317</v>
+        <v>2.863496148912809</v>
       </c>
       <c r="G96">
-        <v>-1.395318429412891</v>
+        <v>-1.55079610204746</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.6366656612305071</v>
       </c>
       <c r="E97">
-        <v>-35.73127998711304</v>
+        <v>-34.96949796591299</v>
       </c>
       <c r="F97">
-        <v>2.237295124236134</v>
+        <v>2.618274546662072</v>
       </c>
       <c r="G97">
-        <v>-1.885457008203908</v>
+        <v>-1.590435037174333</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.3036640576796903</v>
       </c>
       <c r="E98">
-        <v>-38.04310484951464</v>
+        <v>-38.23378085804318</v>
       </c>
       <c r="F98">
-        <v>2.046576783619993</v>
+        <v>2.629008531467548</v>
       </c>
       <c r="G98">
-        <v>-2.067754860022984</v>
+        <v>-1.84078716824996</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.04170844560101612</v>
       </c>
       <c r="E99">
-        <v>-40.07575915308392</v>
+        <v>-40.48122056188162</v>
       </c>
       <c r="F99">
-        <v>1.828575334225247</v>
+        <v>2.630408472378279</v>
       </c>
       <c r="G99">
-        <v>-1.903901918740123</v>
+        <v>-2.087674841253178</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.3981718506721948</v>
       </c>
       <c r="E100">
-        <v>-43.1601207774112</v>
+        <v>-42.11036961918718</v>
       </c>
       <c r="F100">
-        <v>1.682229321907464</v>
+        <v>2.705246497016797</v>
       </c>
       <c r="G100">
-        <v>-2.835282440875197</v>
+        <v>-1.550785659069096</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.7210069405554279</v>
       </c>
       <c r="E101">
-        <v>-44.98650999374419</v>
+        <v>-44.45463729185268</v>
       </c>
       <c r="F101">
-        <v>1.201304058864155</v>
+        <v>2.688422355065939</v>
       </c>
       <c r="G101">
-        <v>-2.013299949341544</v>
+        <v>-1.991737809763539</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.042542276395314</v>
       </c>
       <c r="E102">
-        <v>-47.70653530781222</v>
+        <v>-47.09765791474706</v>
       </c>
       <c r="F102">
-        <v>1.516832516060098</v>
+        <v>2.720528218863643</v>
       </c>
       <c r="G102">
-        <v>-2.19039197644594</v>
+        <v>-2.284331788323378</v>
       </c>
     </row>
   </sheetData>
